--- a/samples/Exchange_Rates_per_USD_sample.xlsx
+++ b/samples/Exchange_Rates_per_USD_sample.xlsx
@@ -434,10 +434,10 @@
         <v>83.4</v>
       </c>
       <c r="D2">
-        <v>83.55</v>
+        <v>84.1</v>
       </c>
       <c r="E2">
-        <v>83.48</v>
+        <v>83.75</v>
       </c>
     </row>
     <row r="3">
@@ -448,13 +448,13 @@
         <v>INR</v>
       </c>
       <c r="C3">
-        <v>83.55</v>
+        <v>84.1</v>
       </c>
       <c r="D3">
-        <v>83.3</v>
+        <v>84.95</v>
       </c>
       <c r="E3">
-        <v>83.42</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="4">
@@ -465,13 +465,13 @@
         <v>INR</v>
       </c>
       <c r="C4">
-        <v>83.3</v>
+        <v>84.95</v>
       </c>
       <c r="D4">
-        <v>83.62</v>
+        <v>85.6</v>
       </c>
       <c r="E4">
-        <v>83.45</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="5">
@@ -482,13 +482,13 @@
         <v>INR</v>
       </c>
       <c r="C5">
-        <v>83.62</v>
+        <v>85.6</v>
       </c>
       <c r="D5">
-        <v>83.9</v>
+        <v>86.4</v>
       </c>
       <c r="E5">
-        <v>83.76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6">
@@ -499,13 +499,13 @@
         <v>INR</v>
       </c>
       <c r="C6">
-        <v>83.9</v>
+        <v>86.4</v>
       </c>
       <c r="D6">
-        <v>84.12</v>
+        <v>86.9</v>
       </c>
       <c r="E6">
-        <v>84.01</v>
+        <v>86.6</v>
       </c>
     </row>
     <row r="7">

--- a/samples/Exchange_Rates_per_USD_sample.xlsx
+++ b/samples/Exchange_Rates_per_USD_sample.xlsx
@@ -468,7 +468,7 @@
         <v>84.95</v>
       </c>
       <c r="D4">
-        <v>85.6</v>
+        <v>85.8</v>
       </c>
       <c r="E4">
         <v>85.3</v>
@@ -482,13 +482,13 @@
         <v>INR</v>
       </c>
       <c r="C5">
-        <v>85.6</v>
+        <v>85.8</v>
       </c>
       <c r="D5">
         <v>86.4</v>
       </c>
       <c r="E5">
-        <v>86</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="6">
@@ -638,10 +638,10 @@
         <v>0.7925</v>
       </c>
       <c r="D14">
-        <v>0.786</v>
+        <v>0.738</v>
       </c>
       <c r="E14">
-        <v>0.789</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="15">
@@ -652,13 +652,13 @@
         <v>GBP</v>
       </c>
       <c r="C15">
-        <v>0.786</v>
+        <v>0.738</v>
       </c>
       <c r="D15">
-        <v>0.7815</v>
+        <v>0.742</v>
       </c>
       <c r="E15">
-        <v>0.7838</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="16">
@@ -669,13 +669,13 @@
         <v>GBP</v>
       </c>
       <c r="C16">
-        <v>0.7815</v>
+        <v>0.742</v>
       </c>
       <c r="D16">
-        <v>0.7842</v>
+        <v>0.747</v>
       </c>
       <c r="E16">
-        <v>0.7829</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="17">
